--- a/機能一覧表.xlsx
+++ b/機能一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F80A688-E1CF-400E-A1FA-B8F21BDFCE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5C416C-0169-4404-921F-112C28739FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="機能一覧表" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">機能一覧表!$A$1:$AC$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">機能一覧表!$A$1:$AC$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">見本!$A$1:$AC$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">原本!$A$1:$AC$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'表紙 '!$A$1:$AF$43</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
   <si>
     <t>機能一覧表</t>
     <rPh sb="0" eb="2">
@@ -418,23 +418,422 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>アカウント更新</t>
-    <rPh sb="5" eb="7">
-      <t>コウシン</t>
+    <t>登録</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>アカウント削除</t>
+    <t>アカウント情報を入力</t>
     <rPh sb="5" eb="7">
-      <t>サクジョ</t>
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>登録</t>
+    <t>データーベースへ登録内容を格納</t>
+    <rPh sb="8" eb="12">
+      <t>トウロクナイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>変更点のみ修正</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンコウテン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データーベースへ更新内容を上書き格納</t>
+    <rPh sb="8" eb="10">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>入力内容をアカウント登録確認画面にて確認</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面にて「登録完了しました」と表示</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>登録済み内容が表示</t>
+    <rPh sb="0" eb="3">
+      <t>トウロクズ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全項目入力されているかや入力形式を判断</t>
+    <rPh sb="0" eb="3">
+      <t>ゼンコウモク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ニュウリョクケイシキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>入力内容をアカウント更新確認画面にて確認</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント更新完了画面にて「更新完了しました」と表示</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>コウシンカンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント更新完了画面にて「エラーが発生したため更新できません」と表示</t>
+    <rPh sb="5" eb="11">
+      <t>コウシンカンリョウガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>情報入力</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウホウニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>入力情報チェック</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>入力情報確認</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ジョウホウカクニン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>情報登録</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウホウトウロク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>登録完了</t>
     <rPh sb="0" eb="2">
       <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>登録時エラー</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント登録完了画面にて「エラーが発生したため登録できません」と表示</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新画面</t>
+    <rPh sb="0" eb="4">
+      <t>コウシンガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント更新・削除</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>情報更新</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウホウコウシン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>入力情報チェック</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新情報確認</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ジョウホウカクニン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新情報格納</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新完了</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新時エラー</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除画面</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除情報確認</t>
+    <rPh sb="0" eb="4">
+      <t>サクジョジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除確認画面にて確認・削除</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除完了</t>
+    <rPh sb="0" eb="4">
+      <t>サクジョカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除情報格納</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>データーベース内「delete_flag」へ1を格納、削除フラグ有効化</t>
+    <rPh sb="7" eb="8">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ユウコウカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除完了画面にて「削除完了しました」と表示</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>サクジョカンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -446,7 +845,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -531,6 +930,12 @@
     <font>
       <sz val="6"/>
       <name val="明朝"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -705,7 +1110,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -765,6 +1170,30 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -795,29 +1224,24 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="6" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="6" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="6" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1313,37 +1737,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
     </row>
     <row r="2" spans="1:173" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1377,10 +1801,10 @@
         <v>2</v>
       </c>
       <c r="AA2" s="3"/>
-      <c r="AB2" s="56" t="s">
+      <c r="AB2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="57"/>
+      <c r="AC2" s="37"/>
     </row>
     <row r="3" spans="1:173" ht="12.75" customHeight="1">
       <c r="A3" s="5"/>
@@ -1408,49 +1832,49 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="59"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="39"/>
     </row>
     <row r="4" spans="1:173" s="9" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="60" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="60" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="60" t="s">
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
-      <c r="X4" s="61"/>
-      <c r="Y4" s="61"/>
-      <c r="Z4" s="61"/>
-      <c r="AA4" s="61"/>
-      <c r="AB4" s="61"/>
-      <c r="AC4" s="62"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="42"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
@@ -2811,37 +3235,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
     </row>
     <row r="2" spans="1:173" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2875,10 +3299,10 @@
         <v>2</v>
       </c>
       <c r="AA2" s="3"/>
-      <c r="AB2" s="56" t="s">
+      <c r="AB2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="57"/>
+      <c r="AC2" s="37"/>
     </row>
     <row r="3" spans="1:173" ht="12.75" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -2908,53 +3332,53 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="58" t="s">
+      <c r="Z3" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="58" t="s">
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="59"/>
+      <c r="AC3" s="39"/>
     </row>
     <row r="4" spans="1:173" s="9" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="60" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="60" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="60" t="s">
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
-      <c r="X4" s="61"/>
-      <c r="Y4" s="61"/>
-      <c r="Z4" s="61"/>
-      <c r="AA4" s="61"/>
-      <c r="AB4" s="61"/>
-      <c r="AC4" s="62"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="42"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
@@ -4731,20 +5155,20 @@
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="E8" s="34"/>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="43"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="51"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -4763,26 +5187,26 @@
     </row>
     <row r="9" spans="1:176" ht="13" customHeight="1">
       <c r="A9" s="23"/>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="49" t="s">
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="51"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="59"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -4801,22 +5225,22 @@
     </row>
     <row r="10" spans="1:176" ht="13" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="54"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="62"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -5031,18 +5455,18 @@
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="44" t="s">
+      <c r="L17" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
-      <c r="U17" s="45"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="AA17" s="7"/>
@@ -5064,16 +5488,16 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="53"/>
+      <c r="U18" s="53"/>
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="AA18" s="7"/>
@@ -5095,16 +5519,16 @@
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="45"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
@@ -5334,10 +5758,10 @@
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="48"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
       <c r="J26" s="10"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -5961,7 +6385,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D119C36D-01FB-4A1A-91F9-F6E2ABED539C}">
-  <dimension ref="A1:FQ42"/>
+  <dimension ref="A1:FQ43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="4.08984375" style="1" customWidth="1"/>
@@ -5972,37 +6396,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
     </row>
     <row r="2" spans="1:173" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -6036,10 +6460,10 @@
         <v>2</v>
       </c>
       <c r="AA2" s="3"/>
-      <c r="AB2" s="56" t="s">
+      <c r="AB2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="57"/>
+      <c r="AC2" s="37"/>
     </row>
     <row r="3" spans="1:173" ht="12.75" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -6069,49 +6493,49 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="59"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="39"/>
     </row>
     <row r="4" spans="1:173" s="9" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="60" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="60" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="60" t="s">
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
-      <c r="X4" s="61"/>
-      <c r="Y4" s="61"/>
-      <c r="Z4" s="61"/>
-      <c r="AA4" s="61"/>
-      <c r="AB4" s="61"/>
-      <c r="AC4" s="62"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="42"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
@@ -6266,34 +6690,38 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="13"/>
-      <c r="J5" s="11"/>
+      <c r="J5" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="13"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="13"/>
+      <c r="P5" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="66"/>
     </row>
     <row r="6" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A6" s="10"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -6302,29 +6730,33 @@
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="13"/>
-      <c r="J6" s="11"/>
+      <c r="J6" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="13"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="13"/>
+      <c r="P6" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="66"/>
     </row>
     <row r="7" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A7" s="10"/>
+      <c r="A7" s="63"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -6333,26 +6765,30 @@
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="13"/>
-      <c r="J7" s="11"/>
+      <c r="J7" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="13"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="13"/>
+      <c r="P7" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="65"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="66"/>
     </row>
     <row r="8" spans="1:173" ht="12.75" customHeight="1">
       <c r="A8" s="10"/>
@@ -6364,26 +6800,30 @@
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="13"/>
-      <c r="J8" s="11"/>
+      <c r="J8" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="13"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="13"/>
+      <c r="P8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="66"/>
     </row>
     <row r="9" spans="1:173" ht="12.75" customHeight="1">
       <c r="A9" s="10"/>
@@ -6395,26 +6835,30 @@
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="13"/>
-      <c r="J9" s="11"/>
+      <c r="J9" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="13"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="11"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="13"/>
+      <c r="P9" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="65"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="65"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="66"/>
     </row>
     <row r="10" spans="1:173" ht="12.75" customHeight="1">
       <c r="A10" s="10"/>
@@ -6426,26 +6870,30 @@
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="11"/>
+      <c r="J10" s="11" t="s">
+        <v>60</v>
+      </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="13"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="13"/>
+      <c r="P10" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="65"/>
+      <c r="U10" s="65"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="66"/>
     </row>
     <row r="11" spans="1:173" ht="12.75" customHeight="1">
       <c r="A11" s="10"/>
@@ -6463,20 +6911,20 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="13"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="13"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="65"/>
+      <c r="U11" s="65"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="66"/>
     </row>
     <row r="12" spans="1:173" ht="12.75" customHeight="1">
       <c r="A12" s="10"/>
@@ -6494,23 +6942,25 @@
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="13"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="13"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="66"/>
     </row>
     <row r="13" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A13" s="10"/>
+      <c r="A13" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -6525,30 +6975,28 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="13"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="13"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="66"/>
     </row>
     <row r="14" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A14" s="10" t="s">
-        <v>40</v>
-      </c>
+      <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
-      <c r="F14" s="10"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="13"/>
@@ -6558,20 +7006,20 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="13"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="13"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="66"/>
     </row>
     <row r="15" spans="1:173" ht="12.75" customHeight="1">
       <c r="A15" s="10"/>
@@ -6579,7 +7027,7 @@
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
-      <c r="F15" s="10"/>
+      <c r="F15" s="12"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="13"/>
@@ -6589,20 +7037,20 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="13"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="13"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="66"/>
     </row>
     <row r="16" spans="1:173" ht="12.75" customHeight="1">
       <c r="A16" s="10"/>
@@ -6620,20 +7068,20 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="13"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="13"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="65"/>
+      <c r="U16" s="65"/>
+      <c r="V16" s="65"/>
+      <c r="W16" s="65"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="65"/>
+      <c r="Z16" s="65"/>
+      <c r="AA16" s="65"/>
+      <c r="AB16" s="65"/>
+      <c r="AC16" s="66"/>
     </row>
     <row r="17" spans="1:29" ht="12.75" customHeight="1">
       <c r="A17" s="10"/>
@@ -6641,7 +7089,7 @@
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="10"/>
+      <c r="F17" s="12"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="13"/>
@@ -6651,20 +7099,20 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="13"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="13"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="65"/>
+      <c r="Z17" s="65"/>
+      <c r="AA17" s="65"/>
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="66"/>
     </row>
     <row r="18" spans="1:29" ht="12.75" customHeight="1">
       <c r="A18" s="10"/>
@@ -6682,20 +7130,20 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="13"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="13"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
+      <c r="Z18" s="65"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="66"/>
     </row>
     <row r="19" spans="1:29" ht="12.75" customHeight="1">
       <c r="A19" s="10"/>
@@ -6703,7 +7151,7 @@
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="10"/>
+      <c r="F19" s="12"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="13"/>
@@ -6713,20 +7161,20 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="13"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="13"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
+      <c r="Z19" s="65"/>
+      <c r="AA19" s="65"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="66"/>
     </row>
     <row r="20" spans="1:29" ht="12.75" customHeight="1">
       <c r="A20" s="10"/>
@@ -6744,20 +7192,20 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="13"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="13"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="65"/>
+      <c r="U20" s="65"/>
+      <c r="V20" s="65"/>
+      <c r="W20" s="65"/>
+      <c r="X20" s="65"/>
+      <c r="Y20" s="65"/>
+      <c r="Z20" s="65"/>
+      <c r="AA20" s="65"/>
+      <c r="AB20" s="65"/>
+      <c r="AC20" s="66"/>
     </row>
     <row r="21" spans="1:29" ht="12.75" customHeight="1">
       <c r="A21" s="10"/>
@@ -6775,20 +7223,20 @@
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
       <c r="O21" s="13"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="11"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="13"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="66"/>
     </row>
     <row r="22" spans="1:29" ht="12.75" customHeight="1">
       <c r="A22" s="10"/>
@@ -6806,25 +7254,23 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
       <c r="O22" s="13"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="13"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="66"/>
     </row>
     <row r="23" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A23" s="10" t="s">
-        <v>41</v>
-      </c>
+      <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -6839,20 +7285,20 @@
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
       <c r="O23" s="13"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="11"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="13"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="66"/>
     </row>
     <row r="24" spans="1:29" ht="12.75" customHeight="1">
       <c r="A24" s="10"/>
@@ -6870,51 +7316,59 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="13"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="11"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="13"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="65"/>
+      <c r="U24" s="65"/>
+      <c r="V24" s="65"/>
+      <c r="W24" s="65"/>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="65"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="66"/>
     </row>
     <row r="25" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A25" s="10"/>
+      <c r="A25" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="10"/>
+      <c r="F25" s="12" t="s">
+        <v>44</v>
+      </c>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="13"/>
-      <c r="J25" s="11"/>
+      <c r="J25" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
       <c r="O25" s="13"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="13"/>
+      <c r="P25" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="65"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="65"/>
+      <c r="Z25" s="65"/>
+      <c r="AA25" s="65"/>
+      <c r="AB25" s="65"/>
+      <c r="AC25" s="66"/>
     </row>
     <row r="26" spans="1:29" ht="12.75" customHeight="1">
       <c r="A26" s="10"/>
@@ -6922,30 +7376,34 @@
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="10"/>
+      <c r="F26" s="12"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="11"/>
+      <c r="J26" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
       <c r="O26" s="13"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="13"/>
+      <c r="P26" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="65"/>
+      <c r="U26" s="65"/>
+      <c r="V26" s="65"/>
+      <c r="W26" s="65"/>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
+      <c r="Z26" s="65"/>
+      <c r="AA26" s="65"/>
+      <c r="AB26" s="65"/>
+      <c r="AC26" s="66"/>
     </row>
     <row r="27" spans="1:29" ht="12.75" customHeight="1">
       <c r="A27" s="10"/>
@@ -6953,30 +7411,34 @@
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="10"/>
+      <c r="F27" s="12"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="11"/>
+      <c r="J27" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
       <c r="O27" s="13"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="11"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="11"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="13"/>
+      <c r="P27" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65"/>
+      <c r="T27" s="65"/>
+      <c r="U27" s="65"/>
+      <c r="V27" s="65"/>
+      <c r="W27" s="65"/>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="65"/>
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="65"/>
+      <c r="AB27" s="65"/>
+      <c r="AC27" s="66"/>
     </row>
     <row r="28" spans="1:29" ht="12.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -6984,63 +7446,69 @@
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="10"/>
+      <c r="F28" s="12"/>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="11"/>
+      <c r="J28" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
       <c r="O28" s="13"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="11"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="13"/>
+      <c r="P28" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="65"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="65"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
+      <c r="Z28" s="65"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="65"/>
+      <c r="AC28" s="66"/>
     </row>
     <row r="29" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A29" s="10" t="s">
-        <v>42</v>
-      </c>
+      <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="10"/>
+      <c r="F29" s="12"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="13"/>
-      <c r="J29" s="11"/>
+      <c r="J29" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="13"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
-      <c r="S29" s="15"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="11"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="11"/>
-      <c r="AB29" s="11"/>
-      <c r="AC29" s="13"/>
+      <c r="P29" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q29" s="65"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="65"/>
+      <c r="U29" s="65"/>
+      <c r="V29" s="65"/>
+      <c r="W29" s="65"/>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="65"/>
+      <c r="Z29" s="65"/>
+      <c r="AA29" s="65"/>
+      <c r="AB29" s="65"/>
+      <c r="AC29" s="66"/>
     </row>
     <row r="30" spans="1:29" ht="12.75" customHeight="1">
       <c r="A30" s="10"/>
@@ -7048,61 +7516,69 @@
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="10"/>
+      <c r="F30" s="12"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="11"/>
+      <c r="J30" s="11" t="s">
+        <v>68</v>
+      </c>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
       <c r="O30" s="13"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="11"/>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="13"/>
-    </row>
-    <row r="31" spans="1:29" ht="12.75" customHeight="1">
+      <c r="P30" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q30" s="65"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="65"/>
+      <c r="T30" s="65"/>
+      <c r="U30" s="65"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="65"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="65"/>
+      <c r="Z30" s="65"/>
+      <c r="AA30" s="65"/>
+      <c r="AB30" s="65"/>
+      <c r="AC30" s="66"/>
+    </row>
+    <row r="31" spans="1:29" ht="12">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="10"/>
+      <c r="F31" s="12"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="13"/>
-      <c r="J31" s="11"/>
+      <c r="J31" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
       <c r="O31" s="13"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="11"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="11"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="11"/>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="13"/>
+      <c r="P31" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="65"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="65"/>
+      <c r="Z31" s="65"/>
+      <c r="AA31" s="65"/>
+      <c r="AB31" s="65"/>
+      <c r="AC31" s="66"/>
     </row>
     <row r="32" spans="1:29" ht="12.75" customHeight="1">
       <c r="A32" s="10"/>
@@ -7110,7 +7586,7 @@
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="10"/>
+      <c r="F32" s="12"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="13"/>
@@ -7120,20 +7596,20 @@
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
       <c r="O32" s="13"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="11"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="11"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="11"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="13"/>
+      <c r="P32" s="67"/>
+      <c r="Q32" s="68"/>
+      <c r="R32" s="68"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="68"/>
+      <c r="U32" s="68"/>
+      <c r="V32" s="68"/>
+      <c r="W32" s="68"/>
+      <c r="X32" s="68"/>
+      <c r="Y32" s="68"/>
+      <c r="Z32" s="68"/>
+      <c r="AA32" s="68"/>
+      <c r="AB32" s="68"/>
+      <c r="AC32" s="69"/>
     </row>
     <row r="33" spans="1:29" ht="12.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -7141,7 +7617,7 @@
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="10"/>
+      <c r="F33" s="12"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
       <c r="I33" s="13"/>
@@ -7151,20 +7627,20 @@
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
       <c r="O33" s="13"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="11"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="11"/>
-      <c r="AB33" s="11"/>
-      <c r="AC33" s="13"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="65"/>
+      <c r="R33" s="65"/>
+      <c r="S33" s="65"/>
+      <c r="T33" s="65"/>
+      <c r="U33" s="65"/>
+      <c r="V33" s="65"/>
+      <c r="W33" s="65"/>
+      <c r="X33" s="65"/>
+      <c r="Y33" s="65"/>
+      <c r="Z33" s="65"/>
+      <c r="AA33" s="65"/>
+      <c r="AB33" s="65"/>
+      <c r="AC33" s="66"/>
     </row>
     <row r="34" spans="1:29" ht="12.75" customHeight="1">
       <c r="A34" s="10"/>
@@ -7172,30 +7648,36 @@
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="10"/>
+      <c r="F34" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="11"/>
+      <c r="J34" s="11" t="s">
+        <v>70</v>
+      </c>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
       <c r="O34" s="13"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="11"/>
-      <c r="V34" s="11"/>
-      <c r="W34" s="11"/>
-      <c r="X34" s="11"/>
-      <c r="Y34" s="11"/>
-      <c r="Z34" s="11"/>
-      <c r="AA34" s="11"/>
-      <c r="AB34" s="11"/>
-      <c r="AC34" s="13"/>
+      <c r="P34" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="65"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="65"/>
+      <c r="W34" s="65"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="65"/>
+      <c r="Z34" s="65"/>
+      <c r="AA34" s="65"/>
+      <c r="AB34" s="65"/>
+      <c r="AC34" s="66"/>
     </row>
     <row r="35" spans="1:29" ht="12.75" customHeight="1">
       <c r="A35" s="10"/>
@@ -7207,26 +7689,30 @@
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="11"/>
+      <c r="J35" s="11" t="s">
+        <v>71</v>
+      </c>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
       <c r="O35" s="13"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="11"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="11"/>
-      <c r="Z35" s="11"/>
-      <c r="AA35" s="11"/>
-      <c r="AB35" s="11"/>
-      <c r="AC35" s="13"/>
+      <c r="P35" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="65"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+      <c r="Z35" s="65"/>
+      <c r="AA35" s="65"/>
+      <c r="AB35" s="65"/>
+      <c r="AC35" s="66"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" customHeight="1">
       <c r="A36" s="10"/>
@@ -7238,26 +7724,30 @@
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="11"/>
+      <c r="J36" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
       <c r="N36" s="11"/>
       <c r="O36" s="13"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
-      <c r="T36" s="11"/>
-      <c r="U36" s="11"/>
-      <c r="V36" s="11"/>
-      <c r="W36" s="11"/>
-      <c r="X36" s="11"/>
-      <c r="Y36" s="11"/>
-      <c r="Z36" s="11"/>
-      <c r="AA36" s="11"/>
-      <c r="AB36" s="11"/>
-      <c r="AC36" s="13"/>
+      <c r="P36" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="65"/>
+      <c r="V36" s="65"/>
+      <c r="W36" s="65"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="65"/>
+      <c r="Z36" s="65"/>
+      <c r="AA36" s="65"/>
+      <c r="AB36" s="65"/>
+      <c r="AC36" s="66"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" customHeight="1">
       <c r="A37" s="10"/>
@@ -7269,26 +7759,30 @@
       <c r="G37" s="11"/>
       <c r="H37" s="11"/>
       <c r="I37" s="13"/>
-      <c r="J37" s="11"/>
+      <c r="J37" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
       <c r="O37" s="13"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
-      <c r="T37" s="11"/>
-      <c r="U37" s="11"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="11"/>
-      <c r="X37" s="11"/>
-      <c r="Y37" s="11"/>
-      <c r="Z37" s="11"/>
-      <c r="AA37" s="11"/>
-      <c r="AB37" s="11"/>
-      <c r="AC37" s="13"/>
+      <c r="P37" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37" s="65"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="65"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="65"/>
+      <c r="V37" s="65"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
+      <c r="Z37" s="65"/>
+      <c r="AA37" s="65"/>
+      <c r="AB37" s="65"/>
+      <c r="AC37" s="66"/>
     </row>
     <row r="38" spans="1:29" ht="12.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -7306,20 +7800,20 @@
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
       <c r="O38" s="13"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
-      <c r="T38" s="11"/>
-      <c r="U38" s="11"/>
-      <c r="V38" s="11"/>
-      <c r="W38" s="11"/>
-      <c r="X38" s="11"/>
-      <c r="Y38" s="11"/>
-      <c r="Z38" s="11"/>
-      <c r="AA38" s="11"/>
-      <c r="AB38" s="11"/>
-      <c r="AC38" s="13"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="65"/>
+      <c r="V38" s="65"/>
+      <c r="W38" s="65"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="65"/>
+      <c r="AA38" s="65"/>
+      <c r="AB38" s="65"/>
+      <c r="AC38" s="66"/>
     </row>
     <row r="39" spans="1:29" ht="12.75" customHeight="1">
       <c r="A39" s="10"/>
@@ -7337,20 +7831,20 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
       <c r="O39" s="13"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="11"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
-      <c r="T39" s="11"/>
-      <c r="U39" s="11"/>
-      <c r="V39" s="11"/>
-      <c r="W39" s="11"/>
-      <c r="X39" s="11"/>
-      <c r="Y39" s="11"/>
-      <c r="Z39" s="11"/>
-      <c r="AA39" s="11"/>
-      <c r="AB39" s="11"/>
-      <c r="AC39" s="13"/>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="65"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="65"/>
+      <c r="X39" s="65"/>
+      <c r="Y39" s="65"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="65"/>
+      <c r="AB39" s="65"/>
+      <c r="AC39" s="66"/>
     </row>
     <row r="40" spans="1:29" ht="12.75" customHeight="1">
       <c r="A40" s="10"/>
@@ -7368,20 +7862,20 @@
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
       <c r="O40" s="13"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
-      <c r="T40" s="11"/>
-      <c r="U40" s="11"/>
-      <c r="V40" s="11"/>
-      <c r="W40" s="11"/>
-      <c r="X40" s="11"/>
-      <c r="Y40" s="11"/>
-      <c r="Z40" s="11"/>
-      <c r="AA40" s="11"/>
-      <c r="AB40" s="11"/>
-      <c r="AC40" s="13"/>
+      <c r="P40" s="64"/>
+      <c r="Q40" s="65"/>
+      <c r="R40" s="65"/>
+      <c r="S40" s="65"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="65"/>
+      <c r="V40" s="65"/>
+      <c r="W40" s="65"/>
+      <c r="X40" s="65"/>
+      <c r="Y40" s="65"/>
+      <c r="Z40" s="65"/>
+      <c r="AA40" s="65"/>
+      <c r="AB40" s="65"/>
+      <c r="AC40" s="66"/>
     </row>
     <row r="41" spans="1:29" ht="12.75" customHeight="1">
       <c r="A41" s="10"/>
@@ -7399,20 +7893,20 @@
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
       <c r="O41" s="13"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
-      <c r="T41" s="11"/>
-      <c r="U41" s="11"/>
-      <c r="V41" s="11"/>
-      <c r="W41" s="11"/>
-      <c r="X41" s="11"/>
-      <c r="Y41" s="11"/>
-      <c r="Z41" s="11"/>
-      <c r="AA41" s="11"/>
-      <c r="AB41" s="11"/>
-      <c r="AC41" s="13"/>
+      <c r="P41" s="64"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="65"/>
+      <c r="X41" s="65"/>
+      <c r="Y41" s="65"/>
+      <c r="Z41" s="65"/>
+      <c r="AA41" s="65"/>
+      <c r="AB41" s="65"/>
+      <c r="AC41" s="66"/>
     </row>
     <row r="42" spans="1:29" ht="12.75" customHeight="1">
       <c r="A42" s="10"/>
@@ -7430,23 +7924,92 @@
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
       <c r="O42" s="13"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
-      <c r="T42" s="11"/>
-      <c r="U42" s="11"/>
-      <c r="V42" s="11"/>
-      <c r="W42" s="11"/>
-      <c r="X42" s="11"/>
-      <c r="Y42" s="11"/>
-      <c r="Z42" s="11"/>
-      <c r="AA42" s="11"/>
-      <c r="AB42" s="11"/>
-      <c r="AC42" s="13"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="65"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="65"/>
+      <c r="V42" s="65"/>
+      <c r="W42" s="65"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="65"/>
+      <c r="AA42" s="65"/>
+      <c r="AB42" s="65"/>
+      <c r="AC42" s="66"/>
+    </row>
+    <row r="43" spans="1:29" ht="12.75" customHeight="1">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="65"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="65"/>
+      <c r="AB43" s="65"/>
+      <c r="AC43" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="46">
+    <mergeCell ref="P27:AC27"/>
+    <mergeCell ref="P7:AC7"/>
+    <mergeCell ref="P28:AC28"/>
+    <mergeCell ref="P31:AC31"/>
+    <mergeCell ref="P26:AC26"/>
+    <mergeCell ref="P10:AC10"/>
+    <mergeCell ref="P11:AC11"/>
+    <mergeCell ref="P41:AC41"/>
+    <mergeCell ref="P42:AC42"/>
+    <mergeCell ref="P43:AC43"/>
+    <mergeCell ref="P36:AC36"/>
+    <mergeCell ref="P37:AC37"/>
+    <mergeCell ref="P38:AC38"/>
+    <mergeCell ref="P39:AC39"/>
+    <mergeCell ref="P40:AC40"/>
+    <mergeCell ref="P29:AC29"/>
+    <mergeCell ref="P30:AC30"/>
+    <mergeCell ref="P33:AC33"/>
+    <mergeCell ref="P34:AC34"/>
+    <mergeCell ref="P35:AC35"/>
+    <mergeCell ref="P21:AC21"/>
+    <mergeCell ref="P22:AC22"/>
+    <mergeCell ref="P23:AC23"/>
+    <mergeCell ref="P24:AC24"/>
+    <mergeCell ref="P25:AC25"/>
+    <mergeCell ref="P18:AC18"/>
+    <mergeCell ref="P19:AC19"/>
+    <mergeCell ref="P20:AC20"/>
+    <mergeCell ref="P13:AC13"/>
+    <mergeCell ref="P14:AC14"/>
+    <mergeCell ref="P15:AC15"/>
+    <mergeCell ref="P16:AC16"/>
+    <mergeCell ref="P17:AC17"/>
+    <mergeCell ref="P5:AC5"/>
+    <mergeCell ref="P6:AC6"/>
+    <mergeCell ref="P8:AC8"/>
+    <mergeCell ref="P9:AC9"/>
+    <mergeCell ref="P12:AC12"/>
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="Z3:AA3"/>

--- a/機能一覧表.xlsx
+++ b/機能一覧表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5C416C-0169-4404-921F-112C28739FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E348D3AB-71EB-42E9-BE40-F84F0683E5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="97">
   <si>
     <t>機能一覧表</t>
     <rPh sb="0" eb="2">
@@ -834,6 +834,248 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索したいアカウント情報の全ての条件を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索条件入力（完全一致）</t>
+    <rPh sb="0" eb="6">
+      <t>ケンサクジョウケンニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カンゼンイッチ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索条件入力（部分一致）</t>
+    <rPh sb="0" eb="6">
+      <t>ケンサクジョウケンニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イッチ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索したいアカウント情報の一部の条件を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あいまい検索</t>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索したいアカウント情報の一部（不完全）の条件を入力</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>フカンゼン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>一覧</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>初期表示</t>
+    <rPh sb="0" eb="4">
+      <t>ショキヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>非表示</t>
+    <rPh sb="0" eb="3">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全アカウント一覧表示</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索結果表示</t>
+    <rPh sb="0" eb="6">
+      <t>ケンサクケッカヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>空欄状態で検索結果表示</t>
+    <rPh sb="0" eb="2">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ケッカヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>条件に合うアカウントを一覧表示</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>検索結果なし</t>
+    <rPh sb="0" eb="4">
+      <t>ケンサクケッカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何も表示されず</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新画面遷移</t>
+    <rPh sb="0" eb="6">
+      <t>コウシンガメンセンイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>該当アカウントの「更新」を押下するとアカウント更新画面へ遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>コウシンガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除画面遷移</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>該当アカウントの「削除」を押下するとアカウント削除画面へ遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -1170,6 +1412,25 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1224,25 +1485,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="6" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="6" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="6" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1737,37 +1979,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
     </row>
     <row r="2" spans="1:173" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1801,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="AA2" s="3"/>
-      <c r="AB2" s="36" t="s">
+      <c r="AB2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="37"/>
+      <c r="AC2" s="44"/>
     </row>
     <row r="3" spans="1:173" ht="12.75" customHeight="1">
       <c r="A3" s="5"/>
@@ -1832,49 +2074,49 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="39"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="46"/>
     </row>
     <row r="4" spans="1:173" s="9" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="40" t="s">
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="40" t="s">
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="40" t="s">
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="42"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="49"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
@@ -3235,37 +3477,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
     </row>
     <row r="2" spans="1:173" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -3299,10 +3541,10 @@
         <v>2</v>
       </c>
       <c r="AA2" s="3"/>
-      <c r="AB2" s="36" t="s">
+      <c r="AB2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="37"/>
+      <c r="AC2" s="44"/>
     </row>
     <row r="3" spans="1:173" ht="12.75" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -3332,53 +3574,53 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="38" t="s">
+      <c r="Z3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="38" t="s">
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="39"/>
+      <c r="AC3" s="46"/>
     </row>
     <row r="4" spans="1:173" s="9" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="40" t="s">
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="40" t="s">
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="40" t="s">
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="42"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="49"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
@@ -5155,20 +5397,20 @@
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="E8" s="34"/>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="51"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="58"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -5187,26 +5429,26 @@
     </row>
     <row r="9" spans="1:176" ht="13" customHeight="1">
       <c r="A9" s="23"/>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="57" t="s">
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58"/>
-      <c r="Q9" s="59"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="66"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -5225,22 +5467,22 @@
     </row>
     <row r="10" spans="1:176" ht="13" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="62"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="69"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -5455,18 +5697,18 @@
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="52" t="s">
+      <c r="L17" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="53"/>
-      <c r="U17" s="53"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="AA17" s="7"/>
@@ -5488,16 +5730,16 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="53"/>
-      <c r="R18" s="53"/>
-      <c r="S18" s="53"/>
-      <c r="T18" s="53"/>
-      <c r="U18" s="53"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="AA18" s="7"/>
@@ -5519,16 +5761,16 @@
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="53"/>
-      <c r="U19" s="53"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
@@ -5758,10 +6000,10 @@
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="63"/>
       <c r="J26" s="10"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -6396,37 +6638,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
     </row>
     <row r="2" spans="1:173" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -6460,10 +6702,10 @@
         <v>2</v>
       </c>
       <c r="AA2" s="3"/>
-      <c r="AB2" s="36" t="s">
+      <c r="AB2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="37"/>
+      <c r="AC2" s="44"/>
     </row>
     <row r="3" spans="1:173" ht="12.75" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -6493,49 +6735,49 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="39"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="46"/>
     </row>
     <row r="4" spans="1:173" s="9" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="40" t="s">
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="40" t="s">
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="40" t="s">
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="42"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="49"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
@@ -6703,25 +6945,25 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="13"/>
-      <c r="P5" s="64" t="s">
+      <c r="P5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="66"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="40"/>
+      <c r="AB5" s="40"/>
+      <c r="AC5" s="41"/>
     </row>
     <row r="6" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A6" s="63"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -6738,25 +6980,25 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="13"/>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="66"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="40"/>
+      <c r="AC6" s="41"/>
     </row>
     <row r="7" spans="1:173" ht="12.75" customHeight="1">
-      <c r="A7" s="63"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -6773,22 +7015,22 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="13"/>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="65"/>
-      <c r="U7" s="65"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="65"/>
-      <c r="X7" s="65"/>
-      <c r="Y7" s="65"/>
-      <c r="Z7" s="65"/>
-      <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
-      <c r="AC7" s="66"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="41"/>
     </row>
     <row r="8" spans="1:173" ht="12.75" customHeight="1">
       <c r="A8" s="10"/>
@@ -6808,22 +7050,22 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="13"/>
-      <c r="P8" s="64" t="s">
+      <c r="P8" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="65"/>
-      <c r="X8" s="65"/>
-      <c r="Y8" s="65"/>
-      <c r="Z8" s="65"/>
-      <c r="AA8" s="65"/>
-      <c r="AB8" s="65"/>
-      <c r="AC8" s="66"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="41"/>
     </row>
     <row r="9" spans="1:173" ht="12.75" customHeight="1">
       <c r="A9" s="10"/>
@@ -6843,22 +7085,22 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="13"/>
-      <c r="P9" s="64" t="s">
+      <c r="P9" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="65"/>
-      <c r="R9" s="65"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="65"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="65"/>
-      <c r="W9" s="65"/>
-      <c r="X9" s="65"/>
-      <c r="Y9" s="65"/>
-      <c r="Z9" s="65"/>
-      <c r="AA9" s="65"/>
-      <c r="AB9" s="65"/>
-      <c r="AC9" s="66"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="41"/>
     </row>
     <row r="10" spans="1:173" ht="12.75" customHeight="1">
       <c r="A10" s="10"/>
@@ -6878,22 +7120,22 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="13"/>
-      <c r="P10" s="64" t="s">
+      <c r="P10" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" s="65"/>
-      <c r="R10" s="65"/>
-      <c r="S10" s="65"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="65"/>
-      <c r="V10" s="65"/>
-      <c r="W10" s="65"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="65"/>
-      <c r="Z10" s="65"/>
-      <c r="AA10" s="65"/>
-      <c r="AB10" s="65"/>
-      <c r="AC10" s="66"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="40"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="40"/>
+      <c r="AB10" s="40"/>
+      <c r="AC10" s="41"/>
     </row>
     <row r="11" spans="1:173" ht="12.75" customHeight="1">
       <c r="A11" s="10"/>
@@ -6911,20 +7153,20 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="13"/>
-      <c r="P11" s="64"/>
-      <c r="Q11" s="65"/>
-      <c r="R11" s="65"/>
-      <c r="S11" s="65"/>
-      <c r="T11" s="65"/>
-      <c r="U11" s="65"/>
-      <c r="V11" s="65"/>
-      <c r="W11" s="65"/>
-      <c r="X11" s="65"/>
-      <c r="Y11" s="65"/>
-      <c r="Z11" s="65"/>
-      <c r="AA11" s="65"/>
-      <c r="AB11" s="65"/>
-      <c r="AC11" s="66"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="41"/>
     </row>
     <row r="12" spans="1:173" ht="12.75" customHeight="1">
       <c r="A12" s="10"/>
@@ -6942,20 +7184,20 @@
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="13"/>
-      <c r="P12" s="64"/>
-      <c r="Q12" s="65"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="65"/>
-      <c r="W12" s="65"/>
-      <c r="X12" s="65"/>
-      <c r="Y12" s="65"/>
-      <c r="Z12" s="65"/>
-      <c r="AA12" s="65"/>
-      <c r="AB12" s="65"/>
-      <c r="AC12" s="66"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
+      <c r="AC12" s="41"/>
     </row>
     <row r="13" spans="1:173" ht="12.75" customHeight="1">
       <c r="A13" s="10" t="s">
@@ -6965,30 +7207,36 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="13"/>
-      <c r="J13" s="11"/>
+      <c r="J13" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="13"/>
-      <c r="P13" s="64"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
-      <c r="V13" s="65"/>
-      <c r="W13" s="65"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="65"/>
-      <c r="Z13" s="65"/>
-      <c r="AA13" s="65"/>
-      <c r="AB13" s="65"/>
-      <c r="AC13" s="66"/>
+      <c r="P13" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="41"/>
     </row>
     <row r="14" spans="1:173" ht="12.75" customHeight="1">
       <c r="A14" s="10"/>
@@ -7000,26 +7248,30 @@
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="13"/>
-      <c r="J14" s="11"/>
+      <c r="J14" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="13"/>
-      <c r="P14" s="64"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="65"/>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="65"/>
-      <c r="Z14" s="65"/>
-      <c r="AA14" s="65"/>
-      <c r="AB14" s="65"/>
-      <c r="AC14" s="66"/>
+      <c r="P14" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="40"/>
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="41"/>
     </row>
     <row r="15" spans="1:173" ht="12.75" customHeight="1">
       <c r="A15" s="10"/>
@@ -7031,26 +7283,30 @@
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="13"/>
-      <c r="J15" s="11"/>
+      <c r="J15" s="11" t="s">
+        <v>82</v>
+      </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="13"/>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="65"/>
-      <c r="X15" s="65"/>
-      <c r="Y15" s="65"/>
-      <c r="Z15" s="65"/>
-      <c r="AA15" s="65"/>
-      <c r="AB15" s="65"/>
-      <c r="AC15" s="66"/>
+      <c r="P15" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="41"/>
     </row>
     <row r="16" spans="1:173" ht="12.75" customHeight="1">
       <c r="A16" s="10"/>
@@ -7068,20 +7324,20 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="13"/>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
-      <c r="R16" s="65"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="65"/>
-      <c r="X16" s="65"/>
-      <c r="Y16" s="65"/>
-      <c r="Z16" s="65"/>
-      <c r="AA16" s="65"/>
-      <c r="AB16" s="65"/>
-      <c r="AC16" s="66"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="40"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="40"/>
+      <c r="AB16" s="40"/>
+      <c r="AC16" s="41"/>
     </row>
     <row r="17" spans="1:29" ht="12.75" customHeight="1">
       <c r="A17" s="10"/>
@@ -7099,20 +7355,20 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="13"/>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-      <c r="Z17" s="65"/>
-      <c r="AA17" s="65"/>
-      <c r="AB17" s="65"/>
-      <c r="AC17" s="66"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="41"/>
     </row>
     <row r="18" spans="1:29" ht="12.75" customHeight="1">
       <c r="A18" s="10"/>
@@ -7120,30 +7376,36 @@
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
-      <c r="F18" s="10"/>
+      <c r="F18" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="11"/>
+      <c r="J18" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="13"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="65"/>
-      <c r="AB18" s="65"/>
-      <c r="AC18" s="66"/>
+      <c r="P18" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
+      <c r="AC18" s="41"/>
     </row>
     <row r="19" spans="1:29" ht="12.75" customHeight="1">
       <c r="A19" s="10"/>
@@ -7155,26 +7417,30 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="13"/>
-      <c r="J19" s="11"/>
+      <c r="J19" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="13"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
-      <c r="Z19" s="65"/>
-      <c r="AA19" s="65"/>
-      <c r="AB19" s="65"/>
-      <c r="AC19" s="66"/>
+      <c r="P19" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="40"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="40"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="41"/>
     </row>
     <row r="20" spans="1:29" ht="12.75" customHeight="1">
       <c r="A20" s="10"/>
@@ -7186,26 +7452,30 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="11"/>
+      <c r="J20" s="11" t="s">
+        <v>88</v>
+      </c>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="13"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="65"/>
-      <c r="X20" s="65"/>
-      <c r="Y20" s="65"/>
-      <c r="Z20" s="65"/>
-      <c r="AA20" s="65"/>
-      <c r="AB20" s="65"/>
-      <c r="AC20" s="66"/>
+      <c r="P20" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40"/>
+      <c r="W20" s="40"/>
+      <c r="X20" s="40"/>
+      <c r="Y20" s="40"/>
+      <c r="Z20" s="40"/>
+      <c r="AA20" s="40"/>
+      <c r="AB20" s="40"/>
+      <c r="AC20" s="41"/>
     </row>
     <row r="21" spans="1:29" ht="12.75" customHeight="1">
       <c r="A21" s="10"/>
@@ -7217,26 +7487,30 @@
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="13"/>
-      <c r="J21" s="11"/>
+      <c r="J21" s="11" t="s">
+        <v>91</v>
+      </c>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
       <c r="O21" s="13"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65"/>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="65"/>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="65"/>
-      <c r="AC21" s="66"/>
+      <c r="P21" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="40"/>
+      <c r="Y21" s="40"/>
+      <c r="Z21" s="40"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="41"/>
     </row>
     <row r="22" spans="1:29" ht="12.75" customHeight="1">
       <c r="A22" s="10"/>
@@ -7248,26 +7522,30 @@
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="11"/>
+      <c r="J22" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
       <c r="O22" s="13"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="66"/>
+      <c r="P22" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="40"/>
+      <c r="Y22" s="40"/>
+      <c r="Z22" s="40"/>
+      <c r="AA22" s="40"/>
+      <c r="AB22" s="40"/>
+      <c r="AC22" s="41"/>
     </row>
     <row r="23" spans="1:29" ht="12.75" customHeight="1">
       <c r="A23" s="10"/>
@@ -7279,26 +7557,30 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="13"/>
-      <c r="J23" s="11"/>
+      <c r="J23" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
       <c r="O23" s="13"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="65"/>
-      <c r="AC23" s="66"/>
+      <c r="P23" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="40"/>
+      <c r="W23" s="40"/>
+      <c r="X23" s="40"/>
+      <c r="Y23" s="40"/>
+      <c r="Z23" s="40"/>
+      <c r="AA23" s="40"/>
+      <c r="AB23" s="40"/>
+      <c r="AC23" s="41"/>
     </row>
     <row r="24" spans="1:29" ht="12.75" customHeight="1">
       <c r="A24" s="10"/>
@@ -7316,94 +7598,90 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="13"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65"/>
-      <c r="T24" s="65"/>
-      <c r="U24" s="65"/>
-      <c r="V24" s="65"/>
-      <c r="W24" s="65"/>
-      <c r="X24" s="65"/>
-      <c r="Y24" s="65"/>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="65"/>
-      <c r="AB24" s="65"/>
-      <c r="AC24" s="66"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="40"/>
+      <c r="Y24" s="40"/>
+      <c r="Z24" s="40"/>
+      <c r="AA24" s="40"/>
+      <c r="AB24" s="40"/>
+      <c r="AC24" s="41"/>
     </row>
     <row r="25" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A25" s="10" t="s">
-        <v>63</v>
-      </c>
+      <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="12" t="s">
-        <v>44</v>
-      </c>
+      <c r="F25" s="10"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="13"/>
-      <c r="J25" s="11" t="s">
-        <v>62</v>
-      </c>
+      <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
       <c r="O25" s="13"/>
-      <c r="P25" s="64" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="65"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
-      <c r="Z25" s="65"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="65"/>
-      <c r="AC25" s="66"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="40"/>
+      <c r="W25" s="40"/>
+      <c r="X25" s="40"/>
+      <c r="Y25" s="40"/>
+      <c r="Z25" s="40"/>
+      <c r="AA25" s="40"/>
+      <c r="AB25" s="40"/>
+      <c r="AC25" s="41"/>
     </row>
     <row r="26" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A26" s="10"/>
+      <c r="A26" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="12" t="s">
+        <v>44</v>
+      </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="13"/>
       <c r="J26" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
       <c r="O26" s="13"/>
-      <c r="P26" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65"/>
-      <c r="T26" s="65"/>
-      <c r="U26" s="65"/>
-      <c r="V26" s="65"/>
-      <c r="W26" s="65"/>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
-      <c r="Z26" s="65"/>
-      <c r="AA26" s="65"/>
-      <c r="AB26" s="65"/>
-      <c r="AC26" s="66"/>
+      <c r="P26" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40"/>
+      <c r="W26" s="40"/>
+      <c r="X26" s="40"/>
+      <c r="Y26" s="40"/>
+      <c r="Z26" s="40"/>
+      <c r="AA26" s="40"/>
+      <c r="AB26" s="40"/>
+      <c r="AC26" s="41"/>
     </row>
     <row r="27" spans="1:29" ht="12.75" customHeight="1">
       <c r="A27" s="10"/>
@@ -7416,29 +7694,29 @@
       <c r="H27" s="11"/>
       <c r="I27" s="13"/>
       <c r="J27" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
       <c r="O27" s="13"/>
-      <c r="P27" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q27" s="65"/>
-      <c r="R27" s="65"/>
-      <c r="S27" s="65"/>
-      <c r="T27" s="65"/>
-      <c r="U27" s="65"/>
-      <c r="V27" s="65"/>
-      <c r="W27" s="65"/>
-      <c r="X27" s="65"/>
-      <c r="Y27" s="65"/>
-      <c r="Z27" s="65"/>
-      <c r="AA27" s="65"/>
-      <c r="AB27" s="65"/>
-      <c r="AC27" s="66"/>
+      <c r="P27" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="40"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="40"/>
+      <c r="Y27" s="40"/>
+      <c r="Z27" s="40"/>
+      <c r="AA27" s="40"/>
+      <c r="AB27" s="40"/>
+      <c r="AC27" s="41"/>
     </row>
     <row r="28" spans="1:29" ht="12.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -7451,29 +7729,29 @@
       <c r="H28" s="11"/>
       <c r="I28" s="13"/>
       <c r="J28" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
       <c r="O28" s="13"/>
-      <c r="P28" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q28" s="65"/>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65"/>
-      <c r="T28" s="65"/>
-      <c r="U28" s="65"/>
-      <c r="V28" s="65"/>
-      <c r="W28" s="65"/>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="65"/>
-      <c r="Z28" s="65"/>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="65"/>
-      <c r="AC28" s="66"/>
+      <c r="P28" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="40"/>
+      <c r="S28" s="40"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="40"/>
+      <c r="W28" s="40"/>
+      <c r="X28" s="40"/>
+      <c r="Y28" s="40"/>
+      <c r="Z28" s="40"/>
+      <c r="AA28" s="40"/>
+      <c r="AB28" s="40"/>
+      <c r="AC28" s="41"/>
     </row>
     <row r="29" spans="1:29" ht="12.75" customHeight="1">
       <c r="A29" s="10"/>
@@ -7486,29 +7764,29 @@
       <c r="H29" s="11"/>
       <c r="I29" s="13"/>
       <c r="J29" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="13"/>
-      <c r="P29" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="65"/>
-      <c r="V29" s="65"/>
-      <c r="W29" s="65"/>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="65"/>
-      <c r="Z29" s="65"/>
-      <c r="AA29" s="65"/>
-      <c r="AB29" s="65"/>
-      <c r="AC29" s="66"/>
+      <c r="P29" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="40"/>
+      <c r="W29" s="40"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="40"/>
+      <c r="AA29" s="40"/>
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="41"/>
     </row>
     <row r="30" spans="1:29" ht="12.75" customHeight="1">
       <c r="A30" s="10"/>
@@ -7521,31 +7799,31 @@
       <c r="H30" s="11"/>
       <c r="I30" s="13"/>
       <c r="J30" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
       <c r="O30" s="13"/>
-      <c r="P30" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="65"/>
-      <c r="V30" s="65"/>
-      <c r="W30" s="65"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="65"/>
-      <c r="Z30" s="65"/>
-      <c r="AA30" s="65"/>
-      <c r="AB30" s="65"/>
-      <c r="AC30" s="66"/>
-    </row>
-    <row r="31" spans="1:29" ht="12">
+      <c r="P30" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="40"/>
+      <c r="S30" s="40"/>
+      <c r="T30" s="40"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="40"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="40"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="40"/>
+      <c r="AB30" s="40"/>
+      <c r="AC30" s="41"/>
+    </row>
+    <row r="31" spans="1:29" ht="12.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7556,31 +7834,31 @@
       <c r="H31" s="11"/>
       <c r="I31" s="13"/>
       <c r="J31" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
       <c r="O31" s="13"/>
-      <c r="P31" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-      <c r="Z31" s="65"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="65"/>
-      <c r="AC31" s="66"/>
-    </row>
-    <row r="32" spans="1:29" ht="12.75" customHeight="1">
+      <c r="P31" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="40"/>
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="40"/>
+      <c r="W31" s="40"/>
+      <c r="X31" s="40"/>
+      <c r="Y31" s="40"/>
+      <c r="Z31" s="40"/>
+      <c r="AA31" s="40"/>
+      <c r="AB31" s="40"/>
+      <c r="AC31" s="41"/>
+    </row>
+    <row r="32" spans="1:29" ht="12">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7590,26 +7868,30 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="13"/>
-      <c r="J32" s="11"/>
+      <c r="J32" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
       <c r="O32" s="13"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="68"/>
-      <c r="R32" s="68"/>
-      <c r="S32" s="68"/>
-      <c r="T32" s="68"/>
-      <c r="U32" s="68"/>
-      <c r="V32" s="68"/>
-      <c r="W32" s="68"/>
-      <c r="X32" s="68"/>
-      <c r="Y32" s="68"/>
-      <c r="Z32" s="68"/>
-      <c r="AA32" s="68"/>
-      <c r="AB32" s="68"/>
-      <c r="AC32" s="69"/>
+      <c r="P32" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="40"/>
+      <c r="S32" s="40"/>
+      <c r="T32" s="40"/>
+      <c r="U32" s="40"/>
+      <c r="V32" s="40"/>
+      <c r="W32" s="40"/>
+      <c r="X32" s="40"/>
+      <c r="Y32" s="40"/>
+      <c r="Z32" s="40"/>
+      <c r="AA32" s="40"/>
+      <c r="AB32" s="40"/>
+      <c r="AC32" s="41"/>
     </row>
     <row r="33" spans="1:29" ht="12.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -7627,20 +7909,20 @@
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
       <c r="O33" s="13"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="65"/>
-      <c r="R33" s="65"/>
-      <c r="S33" s="65"/>
-      <c r="T33" s="65"/>
-      <c r="U33" s="65"/>
-      <c r="V33" s="65"/>
-      <c r="W33" s="65"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="65"/>
-      <c r="Z33" s="65"/>
-      <c r="AA33" s="65"/>
-      <c r="AB33" s="65"/>
-      <c r="AC33" s="66"/>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="37"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="37"/>
+      <c r="X33" s="37"/>
+      <c r="Y33" s="37"/>
+      <c r="Z33" s="37"/>
+      <c r="AA33" s="37"/>
+      <c r="AB33" s="37"/>
+      <c r="AC33" s="38"/>
     </row>
     <row r="34" spans="1:29" ht="12.75" customHeight="1">
       <c r="A34" s="10"/>
@@ -7648,36 +7930,30 @@
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="12" t="s">
-        <v>47</v>
-      </c>
+      <c r="F34" s="12"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="11" t="s">
-        <v>70</v>
-      </c>
+      <c r="J34" s="11"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
       <c r="O34" s="13"/>
-      <c r="P34" s="64" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="65"/>
-      <c r="T34" s="65"/>
-      <c r="U34" s="65"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="65"/>
-      <c r="X34" s="65"/>
-      <c r="Y34" s="65"/>
-      <c r="Z34" s="65"/>
-      <c r="AA34" s="65"/>
-      <c r="AB34" s="65"/>
-      <c r="AC34" s="66"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="40"/>
+      <c r="S34" s="40"/>
+      <c r="T34" s="40"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="X34" s="40"/>
+      <c r="Y34" s="40"/>
+      <c r="Z34" s="40"/>
+      <c r="AA34" s="40"/>
+      <c r="AB34" s="40"/>
+      <c r="AC34" s="41"/>
     </row>
     <row r="35" spans="1:29" ht="12.75" customHeight="1">
       <c r="A35" s="10"/>
@@ -7685,34 +7961,36 @@
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="10"/>
+      <c r="F35" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
       <c r="I35" s="13"/>
       <c r="J35" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
       <c r="O35" s="13"/>
-      <c r="P35" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="65"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
-      <c r="Z35" s="65"/>
-      <c r="AA35" s="65"/>
-      <c r="AB35" s="65"/>
-      <c r="AC35" s="66"/>
+      <c r="P35" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="40"/>
+      <c r="V35" s="40"/>
+      <c r="W35" s="40"/>
+      <c r="X35" s="40"/>
+      <c r="Y35" s="40"/>
+      <c r="Z35" s="40"/>
+      <c r="AA35" s="40"/>
+      <c r="AB35" s="40"/>
+      <c r="AC35" s="41"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" customHeight="1">
       <c r="A36" s="10"/>
@@ -7725,29 +8003,29 @@
       <c r="H36" s="11"/>
       <c r="I36" s="13"/>
       <c r="J36" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
       <c r="N36" s="11"/>
       <c r="O36" s="13"/>
-      <c r="P36" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="65"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="65"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
-      <c r="Z36" s="65"/>
-      <c r="AA36" s="65"/>
-      <c r="AB36" s="65"/>
-      <c r="AC36" s="66"/>
+      <c r="P36" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="40"/>
+      <c r="S36" s="40"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="40"/>
+      <c r="Y36" s="40"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="40"/>
+      <c r="AB36" s="40"/>
+      <c r="AC36" s="41"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" customHeight="1">
       <c r="A37" s="10"/>
@@ -7760,29 +8038,29 @@
       <c r="H37" s="11"/>
       <c r="I37" s="13"/>
       <c r="J37" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
       <c r="O37" s="13"/>
-      <c r="P37" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="65"/>
-      <c r="S37" s="65"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="65"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="65"/>
-      <c r="X37" s="65"/>
-      <c r="Y37" s="65"/>
-      <c r="Z37" s="65"/>
-      <c r="AA37" s="65"/>
-      <c r="AB37" s="65"/>
-      <c r="AC37" s="66"/>
+      <c r="P37" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="40"/>
+      <c r="S37" s="40"/>
+      <c r="T37" s="40"/>
+      <c r="U37" s="40"/>
+      <c r="V37" s="40"/>
+      <c r="W37" s="40"/>
+      <c r="X37" s="40"/>
+      <c r="Y37" s="40"/>
+      <c r="Z37" s="40"/>
+      <c r="AA37" s="40"/>
+      <c r="AB37" s="40"/>
+      <c r="AC37" s="41"/>
     </row>
     <row r="38" spans="1:29" ht="12.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -7794,26 +8072,30 @@
       <c r="G38" s="11"/>
       <c r="H38" s="11"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="11"/>
+      <c r="J38" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
       <c r="O38" s="13"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="65"/>
-      <c r="T38" s="65"/>
-      <c r="U38" s="65"/>
-      <c r="V38" s="65"/>
-      <c r="W38" s="65"/>
-      <c r="X38" s="65"/>
-      <c r="Y38" s="65"/>
-      <c r="Z38" s="65"/>
-      <c r="AA38" s="65"/>
-      <c r="AB38" s="65"/>
-      <c r="AC38" s="66"/>
+      <c r="P38" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="40"/>
+      <c r="S38" s="40"/>
+      <c r="T38" s="40"/>
+      <c r="U38" s="40"/>
+      <c r="V38" s="40"/>
+      <c r="W38" s="40"/>
+      <c r="X38" s="40"/>
+      <c r="Y38" s="40"/>
+      <c r="Z38" s="40"/>
+      <c r="AA38" s="40"/>
+      <c r="AB38" s="40"/>
+      <c r="AC38" s="41"/>
     </row>
     <row r="39" spans="1:29" ht="12.75" customHeight="1">
       <c r="A39" s="10"/>
@@ -7831,20 +8113,20 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
       <c r="O39" s="13"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="65"/>
-      <c r="X39" s="65"/>
-      <c r="Y39" s="65"/>
-      <c r="Z39" s="65"/>
-      <c r="AA39" s="65"/>
-      <c r="AB39" s="65"/>
-      <c r="AC39" s="66"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="40"/>
+      <c r="S39" s="40"/>
+      <c r="T39" s="40"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="40"/>
+      <c r="W39" s="40"/>
+      <c r="X39" s="40"/>
+      <c r="Y39" s="40"/>
+      <c r="Z39" s="40"/>
+      <c r="AA39" s="40"/>
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="41"/>
     </row>
     <row r="40" spans="1:29" ht="12.75" customHeight="1">
       <c r="A40" s="10"/>
@@ -7862,20 +8144,20 @@
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
       <c r="O40" s="13"/>
-      <c r="P40" s="64"/>
-      <c r="Q40" s="65"/>
-      <c r="R40" s="65"/>
-      <c r="S40" s="65"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="65"/>
-      <c r="W40" s="65"/>
-      <c r="X40" s="65"/>
-      <c r="Y40" s="65"/>
-      <c r="Z40" s="65"/>
-      <c r="AA40" s="65"/>
-      <c r="AB40" s="65"/>
-      <c r="AC40" s="66"/>
+      <c r="P40" s="39"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="40"/>
+      <c r="S40" s="40"/>
+      <c r="T40" s="40"/>
+      <c r="U40" s="40"/>
+      <c r="V40" s="40"/>
+      <c r="W40" s="40"/>
+      <c r="X40" s="40"/>
+      <c r="Y40" s="40"/>
+      <c r="Z40" s="40"/>
+      <c r="AA40" s="40"/>
+      <c r="AB40" s="40"/>
+      <c r="AC40" s="41"/>
     </row>
     <row r="41" spans="1:29" ht="12.75" customHeight="1">
       <c r="A41" s="10"/>
@@ -7893,20 +8175,20 @@
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
       <c r="O41" s="13"/>
-      <c r="P41" s="64"/>
-      <c r="Q41" s="65"/>
-      <c r="R41" s="65"/>
-      <c r="S41" s="65"/>
-      <c r="T41" s="65"/>
-      <c r="U41" s="65"/>
-      <c r="V41" s="65"/>
-      <c r="W41" s="65"/>
-      <c r="X41" s="65"/>
-      <c r="Y41" s="65"/>
-      <c r="Z41" s="65"/>
-      <c r="AA41" s="65"/>
-      <c r="AB41" s="65"/>
-      <c r="AC41" s="66"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="40"/>
+      <c r="S41" s="40"/>
+      <c r="T41" s="40"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="40"/>
+      <c r="Y41" s="40"/>
+      <c r="Z41" s="40"/>
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="40"/>
+      <c r="AC41" s="41"/>
     </row>
     <row r="42" spans="1:29" ht="12.75" customHeight="1">
       <c r="A42" s="10"/>
@@ -7924,20 +8206,20 @@
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
       <c r="O42" s="13"/>
-      <c r="P42" s="64"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="65"/>
-      <c r="S42" s="65"/>
-      <c r="T42" s="65"/>
-      <c r="U42" s="65"/>
-      <c r="V42" s="65"/>
-      <c r="W42" s="65"/>
-      <c r="X42" s="65"/>
-      <c r="Y42" s="65"/>
-      <c r="Z42" s="65"/>
-      <c r="AA42" s="65"/>
-      <c r="AB42" s="65"/>
-      <c r="AC42" s="66"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="40"/>
+      <c r="S42" s="40"/>
+      <c r="T42" s="40"/>
+      <c r="U42" s="40"/>
+      <c r="V42" s="40"/>
+      <c r="W42" s="40"/>
+      <c r="X42" s="40"/>
+      <c r="Y42" s="40"/>
+      <c r="Z42" s="40"/>
+      <c r="AA42" s="40"/>
+      <c r="AB42" s="40"/>
+      <c r="AC42" s="41"/>
     </row>
     <row r="43" spans="1:29" ht="12.75" customHeight="1">
       <c r="A43" s="10"/>
@@ -7955,61 +8237,23 @@
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
       <c r="O43" s="13"/>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="65"/>
-      <c r="Y43" s="65"/>
-      <c r="Z43" s="65"/>
-      <c r="AA43" s="65"/>
-      <c r="AB43" s="65"/>
-      <c r="AC43" s="66"/>
+      <c r="P43" s="39"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="40"/>
+      <c r="S43" s="40"/>
+      <c r="T43" s="40"/>
+      <c r="U43" s="40"/>
+      <c r="V43" s="40"/>
+      <c r="W43" s="40"/>
+      <c r="X43" s="40"/>
+      <c r="Y43" s="40"/>
+      <c r="Z43" s="40"/>
+      <c r="AA43" s="40"/>
+      <c r="AB43" s="40"/>
+      <c r="AC43" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="P27:AC27"/>
-    <mergeCell ref="P7:AC7"/>
-    <mergeCell ref="P28:AC28"/>
-    <mergeCell ref="P31:AC31"/>
-    <mergeCell ref="P26:AC26"/>
-    <mergeCell ref="P10:AC10"/>
-    <mergeCell ref="P11:AC11"/>
-    <mergeCell ref="P41:AC41"/>
-    <mergeCell ref="P42:AC42"/>
-    <mergeCell ref="P43:AC43"/>
-    <mergeCell ref="P36:AC36"/>
-    <mergeCell ref="P37:AC37"/>
-    <mergeCell ref="P38:AC38"/>
-    <mergeCell ref="P39:AC39"/>
-    <mergeCell ref="P40:AC40"/>
-    <mergeCell ref="P29:AC29"/>
-    <mergeCell ref="P30:AC30"/>
-    <mergeCell ref="P33:AC33"/>
-    <mergeCell ref="P34:AC34"/>
-    <mergeCell ref="P35:AC35"/>
-    <mergeCell ref="P21:AC21"/>
-    <mergeCell ref="P22:AC22"/>
-    <mergeCell ref="P23:AC23"/>
-    <mergeCell ref="P24:AC24"/>
-    <mergeCell ref="P25:AC25"/>
-    <mergeCell ref="P18:AC18"/>
-    <mergeCell ref="P19:AC19"/>
-    <mergeCell ref="P20:AC20"/>
-    <mergeCell ref="P13:AC13"/>
-    <mergeCell ref="P14:AC14"/>
-    <mergeCell ref="P15:AC15"/>
-    <mergeCell ref="P16:AC16"/>
-    <mergeCell ref="P17:AC17"/>
-    <mergeCell ref="P5:AC5"/>
-    <mergeCell ref="P6:AC6"/>
-    <mergeCell ref="P8:AC8"/>
-    <mergeCell ref="P9:AC9"/>
-    <mergeCell ref="P12:AC12"/>
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="Z3:AA3"/>
@@ -8018,6 +8262,44 @@
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="J4:O4"/>
     <mergeCell ref="P4:AC4"/>
+    <mergeCell ref="P17:AC17"/>
+    <mergeCell ref="P5:AC5"/>
+    <mergeCell ref="P6:AC6"/>
+    <mergeCell ref="P8:AC8"/>
+    <mergeCell ref="P9:AC9"/>
+    <mergeCell ref="P12:AC12"/>
+    <mergeCell ref="P34:AC34"/>
+    <mergeCell ref="P35:AC35"/>
+    <mergeCell ref="P36:AC36"/>
+    <mergeCell ref="P21:AC21"/>
+    <mergeCell ref="P22:AC22"/>
+    <mergeCell ref="P24:AC24"/>
+    <mergeCell ref="P25:AC25"/>
+    <mergeCell ref="P26:AC26"/>
+    <mergeCell ref="P23:AC23"/>
+    <mergeCell ref="P42:AC42"/>
+    <mergeCell ref="P43:AC43"/>
+    <mergeCell ref="P37:AC37"/>
+    <mergeCell ref="P38:AC38"/>
+    <mergeCell ref="P39:AC39"/>
+    <mergeCell ref="P40:AC40"/>
+    <mergeCell ref="P41:AC41"/>
+    <mergeCell ref="P28:AC28"/>
+    <mergeCell ref="P7:AC7"/>
+    <mergeCell ref="P29:AC29"/>
+    <mergeCell ref="P32:AC32"/>
+    <mergeCell ref="P27:AC27"/>
+    <mergeCell ref="P10:AC10"/>
+    <mergeCell ref="P11:AC11"/>
+    <mergeCell ref="P30:AC30"/>
+    <mergeCell ref="P31:AC31"/>
+    <mergeCell ref="P18:AC18"/>
+    <mergeCell ref="P19:AC19"/>
+    <mergeCell ref="P20:AC20"/>
+    <mergeCell ref="P13:AC13"/>
+    <mergeCell ref="P14:AC14"/>
+    <mergeCell ref="P15:AC15"/>
+    <mergeCell ref="P16:AC16"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
